--- a/docs/demo/prenos-2027/prenos-2026-2027.xlsx
+++ b/docs/demo/prenos-2027/prenos-2026-2027.xlsx
@@ -419,10 +419,10 @@
         <v>Вкупно затворање 31.12.2026 (класи 0,1,2,3,6,9)</v>
       </c>
       <c r="B2" t="str">
-        <v>3.160.510,00</v>
+        <v>1.642.510,00</v>
       </c>
       <c r="C2" t="str">
-        <v>3.160.510,00</v>
+        <v>1.642.510,00</v>
       </c>
       <c r="D2" t="str">
         <v>1.582.510,00</v>
@@ -436,10 +436,10 @@
         <v>Вкупно почетна 01.01.2027 (налог 0)</v>
       </c>
       <c r="B3" t="str">
-        <v>3.160.510,00</v>
+        <v>1.642.510,00</v>
       </c>
       <c r="C3" t="str">
-        <v>3.160.510,00</v>
+        <v>1.642.510,00</v>
       </c>
       <c r="D3" t="str">
         <v>1.582.510,00</v>
@@ -578,13 +578,13 @@
         <v>Побарување од купувачи од продажба на добра</v>
       </c>
       <c r="C7" t="str">
-        <v>МАРКЕТ ПЛУС ДООЕЛ Скопје</v>
+        <v>АГРО ЕКСПОРТ ДОО Струмица</v>
       </c>
       <c r="F7" t="str">
-        <v>334.760,00</v>
+        <v>202.980,00</v>
       </c>
       <c r="H7" t="str">
-        <v>334.760,00</v>
+        <v>202.980,00</v>
       </c>
       <c r="J7" t="str">
         <v>✓ пренесено</v>
@@ -598,13 +598,13 @@
         <v>Побарување од купувачи од продажба на добра</v>
       </c>
       <c r="C8" t="str">
-        <v>АГРО ЕКСПОРТ ДОО Струмица</v>
+        <v>МАРКЕТ ПЛУС ДООЕЛ Скопје</v>
       </c>
       <c r="F8" t="str">
-        <v>202.980,00</v>
+        <v>334.760,00</v>
       </c>
       <c r="H8" t="str">
-        <v>202.980,00</v>
+        <v>334.760,00</v>
       </c>
       <c r="J8" t="str">
         <v>✓ пренесено</v>
@@ -644,7 +644,7 @@
         <v>—</v>
       </c>
       <c r="J10" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (нулто салдо)</v>
       </c>
       <c r="K10" t="str">
         <v>нулто салдо на 31.12 – нема што да се пренесе</v>
@@ -675,13 +675,13 @@
         <v>Обврски спрема добавувачи врз основа на набавка на добра</v>
       </c>
       <c r="C12" t="str">
-        <v>МЕТАЛ КОМЕРЦ ДОО Велес</v>
+        <v>ЕВН МАКЕДОНИЈА АД Скопје</v>
       </c>
       <c r="G12" t="str">
-        <v>247.600,00</v>
+        <v>30.680,00</v>
       </c>
       <c r="I12" t="str">
-        <v>247.600,00</v>
+        <v>30.680,00</v>
       </c>
       <c r="J12" t="str">
         <v>✓ пренесено</v>
@@ -715,13 +715,13 @@
         <v>Обврски спрема добавувачи врз основа на набавка на добра</v>
       </c>
       <c r="C14" t="str">
-        <v>ЕВН МАКЕДОНИЈА АД Скопје</v>
+        <v>МЕТАЛ КОМЕРЦ ДОО Велес</v>
       </c>
       <c r="G14" t="str">
-        <v>30.680,00</v>
+        <v>247.600,00</v>
       </c>
       <c r="I14" t="str">
-        <v>30.680,00</v>
+        <v>247.600,00</v>
       </c>
       <c r="J14" t="str">
         <v>✓ пренесено</v>
@@ -741,7 +741,7 @@
         <v>—</v>
       </c>
       <c r="J15" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (нулто салдо)</v>
       </c>
       <c r="K15" t="str">
         <v>нулто салдо на 31.12 – нема што да се пренесе</v>
@@ -837,7 +837,7 @@
         <v>2343</v>
       </c>
       <c r="B21" t="str">
-        <v>Обврски за допо;нителен придонес за здраствено осигурување</v>
+        <v>Обврски за дополнителен придонес за здраствено осигурување</v>
       </c>
       <c r="G21" t="str">
         <v>592,00</v>
@@ -880,7 +880,7 @@
         <v>—</v>
       </c>
       <c r="J23" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (нулто салдо)</v>
       </c>
       <c r="K23" t="str">
         <v>нулто салдо на 31.12 – нема што да се пренесе</v>
@@ -954,7 +954,7 @@
         <v>—</v>
       </c>
       <c r="J27" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K27" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -974,7 +974,7 @@
         <v>—</v>
       </c>
       <c r="J28" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K28" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -994,7 +994,7 @@
         <v>—</v>
       </c>
       <c r="J29" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K29" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -1014,7 +1014,7 @@
         <v>—</v>
       </c>
       <c r="J30" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K30" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -1034,7 +1034,7 @@
         <v>—</v>
       </c>
       <c r="J31" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K31" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -1054,7 +1054,7 @@
         <v>—</v>
       </c>
       <c r="J32" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K32" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -1074,7 +1074,7 @@
         <v>—</v>
       </c>
       <c r="J33" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K33" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -1094,7 +1094,7 @@
         <v>—</v>
       </c>
       <c r="J34" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K34" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -1114,7 +1114,7 @@
         <v>—</v>
       </c>
       <c r="J35" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K35" t="str">
         <v>класа 4 (трошоци) – се затвора на 8000, не се пренесува</v>
@@ -1134,7 +1134,7 @@
         <v>—</v>
       </c>
       <c r="J36" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K36" t="str">
         <v>класа 7 (приходи и расходи) – се затвора на 8000, не се пренесува</v>
@@ -1154,7 +1154,7 @@
         <v>—</v>
       </c>
       <c r="J37" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K37" t="str">
         <v>класа 8 (резултат) – се затвора на 951 / 961, не се пренесува</v>
@@ -1174,7 +1174,7 @@
         <v>—</v>
       </c>
       <c r="J38" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K38" t="str">
         <v>класа 8 (резултат) – се затвора на 951 / 961, не се пренесува</v>
@@ -1194,7 +1194,7 @@
         <v>—</v>
       </c>
       <c r="J39" t="str">
-        <v>⚠ не е пренесено</v>
+        <v>— не се пренесува (по закон)</v>
       </c>
       <c r="K39" t="str">
         <v>класа 8 (резултат) – се затвора на 951 / 961, не се пренесува</v>
@@ -1248,10 +1248,16 @@
         <v>1.518.000,00</v>
       </c>
       <c r="H42" t="str">
-        <v>1.518.000,00</v>
+        <v>—</v>
+      </c>
+      <c r="I42" t="str">
+        <v>—</v>
       </c>
       <c r="J42" t="str">
-        <v>✓ пренесено</v>
+        <v>— не се пренесува (статистичка)</v>
+      </c>
+      <c r="K42" t="str">
+        <v>статистичка сметка (основица за ДДВ) – не се пренесува</v>
       </c>
     </row>
     <row r="43">
@@ -1264,11 +1270,17 @@
       <c r="G43" t="str">
         <v>1.518.000,00</v>
       </c>
+      <c r="H43" t="str">
+        <v>—</v>
+      </c>
       <c r="I43" t="str">
-        <v>1.518.000,00</v>
+        <v>—</v>
       </c>
       <c r="J43" t="str">
-        <v>✓ пренесено</v>
+        <v>— не се пренесува (статистичка)</v>
+      </c>
+      <c r="K43" t="str">
+        <v>статистичка сметка (основица за ДДВ) – не се пренесува</v>
       </c>
     </row>
   </sheetData>
